--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/35.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/35.xlsx
@@ -426,13 +426,13 @@
         <v>-18.97434404018366</v>
       </c>
       <c r="E2">
-        <v>-10.72894873668636</v>
+        <v>-11.85476360278527</v>
       </c>
       <c r="F2">
-        <v>1.699938990514923</v>
+        <v>1.502777106278204</v>
       </c>
       <c r="G2">
-        <v>-14.1411222223957</v>
+        <v>-15.15850086952406</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.42386540290474</v>
       </c>
       <c r="E3">
-        <v>-12.1082947485787</v>
+        <v>-12.61884396515148</v>
       </c>
       <c r="F3">
-        <v>1.6728465334195</v>
+        <v>1.750774366694614</v>
       </c>
       <c r="G3">
-        <v>-14.02865140351727</v>
+        <v>-15.52297703594289</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.79353040402299</v>
       </c>
       <c r="E4">
-        <v>-12.07588898857981</v>
+        <v>-12.03716600734023</v>
       </c>
       <c r="F4">
-        <v>1.409088231732638</v>
+        <v>2.135573727792598</v>
       </c>
       <c r="G4">
-        <v>-12.85341601343985</v>
+        <v>-13.68077100188681</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.14903238316235</v>
       </c>
       <c r="E5">
-        <v>-12.845272194009</v>
+        <v>-13.28001022721936</v>
       </c>
       <c r="F5">
-        <v>1.290706214553539</v>
+        <v>1.824590899413247</v>
       </c>
       <c r="G5">
-        <v>-13.33320675735534</v>
+        <v>-14.66520309980834</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.50122929806707</v>
       </c>
       <c r="E6">
-        <v>-13.75449467679505</v>
+        <v>-14.07418682784054</v>
       </c>
       <c r="F6">
-        <v>1.752920288210034</v>
+        <v>2.115885095851855</v>
       </c>
       <c r="G6">
-        <v>-12.76071742779472</v>
+        <v>-14.02253682590624</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.85216523541946</v>
       </c>
       <c r="E7">
-        <v>-14.26500313710175</v>
+        <v>-14.39215363028912</v>
       </c>
       <c r="F7">
-        <v>2.04322941956924</v>
+        <v>2.247400786187693</v>
       </c>
       <c r="G7">
-        <v>-11.33135297521345</v>
+        <v>-13.84327244022747</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.2158650989198</v>
       </c>
       <c r="E8">
-        <v>-13.86529737881473</v>
+        <v>-14.7457866940221</v>
       </c>
       <c r="F8">
-        <v>1.941758214155203</v>
+        <v>1.998155565509917</v>
       </c>
       <c r="G8">
-        <v>-11.97385041129304</v>
+        <v>-12.4302951880656</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.60167924168394</v>
       </c>
       <c r="E9">
-        <v>-14.90664261924856</v>
+        <v>-15.44289545428887</v>
       </c>
       <c r="F9">
-        <v>1.991603774137744</v>
+        <v>2.024519517884238</v>
       </c>
       <c r="G9">
-        <v>-10.75747652707187</v>
+        <v>-12.28996447320143</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.98940257328588</v>
       </c>
       <c r="E10">
-        <v>-15.68410462230743</v>
+        <v>-17.88582151399271</v>
       </c>
       <c r="F10">
-        <v>2.243411430986701</v>
+        <v>2.06970106394581</v>
       </c>
       <c r="G10">
-        <v>-11.11700177263672</v>
+        <v>-10.98927099409502</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.39053786120712</v>
       </c>
       <c r="E11">
-        <v>-16.11507043666941</v>
+        <v>-15.93138194549627</v>
       </c>
       <c r="F11">
-        <v>2.274743468817755</v>
+        <v>2.246707122996731</v>
       </c>
       <c r="G11">
-        <v>-10.92009052396087</v>
+        <v>-11.78546712792636</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.79914640412941</v>
       </c>
       <c r="E12">
-        <v>-16.4946290140963</v>
+        <v>-16.19812264997008</v>
       </c>
       <c r="F12">
-        <v>2.122326027809947</v>
+        <v>2.132724640850723</v>
       </c>
       <c r="G12">
-        <v>-9.872580946606837</v>
+        <v>-10.89672138299915</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.1942329195294</v>
       </c>
       <c r="E13">
-        <v>-16.95570465213528</v>
+        <v>-19.43288861770715</v>
       </c>
       <c r="F13">
-        <v>2.675199346595774</v>
+        <v>2.662330152326913</v>
       </c>
       <c r="G13">
-        <v>-9.532124443348188</v>
+        <v>-10.87587156719282</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.58995894495201</v>
       </c>
       <c r="E14">
-        <v>-18.79030721296674</v>
+        <v>-20.01530018830764</v>
       </c>
       <c r="F14">
-        <v>2.865527539807371</v>
+        <v>2.807098293763148</v>
       </c>
       <c r="G14">
-        <v>-9.149660427741727</v>
+        <v>-10.14972326642692</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.98001480670728</v>
       </c>
       <c r="E15">
-        <v>-19.25242440002748</v>
+        <v>-20.33648220730166</v>
       </c>
       <c r="F15">
-        <v>3.072842562667972</v>
+        <v>2.977264326965286</v>
       </c>
       <c r="G15">
-        <v>-9.268273963868275</v>
+        <v>-9.980951654834879</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.35226405502846</v>
       </c>
       <c r="E16">
-        <v>-21.08970781747148</v>
+        <v>-21.42333408303858</v>
       </c>
       <c r="F16">
-        <v>3.432581361360043</v>
+        <v>3.687594438981848</v>
       </c>
       <c r="G16">
-        <v>-8.11216525064399</v>
+        <v>-9.451827161293165</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.72234417967003</v>
       </c>
       <c r="E17">
-        <v>-20.57198096959655</v>
+        <v>-23.17074540532635</v>
       </c>
       <c r="F17">
-        <v>3.548773113258088</v>
+        <v>3.461688292379904</v>
       </c>
       <c r="G17">
-        <v>-8.600805082785957</v>
+        <v>-9.311609004977333</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.088828048135504</v>
       </c>
       <c r="E18">
-        <v>-22.963314124931</v>
+        <v>-23.19855023573345</v>
       </c>
       <c r="F18">
-        <v>3.869886908378506</v>
+        <v>3.794006806852056</v>
       </c>
       <c r="G18">
-        <v>-8.385126351447978</v>
+        <v>-8.183467780468813</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.451793429251072</v>
       </c>
       <c r="E19">
-        <v>-22.91211066932627</v>
+        <v>-23.73017497033792</v>
       </c>
       <c r="F19">
-        <v>3.806901340415564</v>
+        <v>4.008228371209889</v>
       </c>
       <c r="G19">
-        <v>-6.940354619926943</v>
+        <v>-9.082979419489726</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.831360869367281</v>
       </c>
       <c r="E20">
-        <v>-24.21392014925929</v>
+        <v>-24.96601364092719</v>
       </c>
       <c r="F20">
-        <v>4.166215705922297</v>
+        <v>4.518791402758835</v>
       </c>
       <c r="G20">
-        <v>-7.391773988570884</v>
+        <v>-7.647450731114336</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.230703957399228</v>
       </c>
       <c r="E21">
-        <v>-24.86952091677175</v>
+        <v>-25.69502097210399</v>
       </c>
       <c r="F21">
-        <v>4.282078046989931</v>
+        <v>4.397401928046317</v>
       </c>
       <c r="G21">
-        <v>-7.535435112247557</v>
+        <v>-7.807108410836768</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.657297378551862</v>
       </c>
       <c r="E22">
-        <v>-25.48175701718676</v>
+        <v>-24.97430980530924</v>
       </c>
       <c r="F22">
-        <v>4.329747595044658</v>
+        <v>3.883894787200568</v>
       </c>
       <c r="G22">
-        <v>-6.284532238051781</v>
+        <v>-6.569139838062926</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.1311609660054</v>
       </c>
       <c r="E23">
-        <v>-25.42354348381815</v>
+        <v>-25.99490557783993</v>
       </c>
       <c r="F23">
-        <v>4.577185807272918</v>
+        <v>4.374598146569904</v>
       </c>
       <c r="G23">
-        <v>-6.130624975931064</v>
+        <v>-6.794180792185963</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.658010751443303</v>
       </c>
       <c r="E24">
-        <v>-26.1923153452563</v>
+        <v>-25.40926973374598</v>
       </c>
       <c r="F24">
-        <v>4.692265797618325</v>
+        <v>4.395301934002443</v>
       </c>
       <c r="G24">
-        <v>-6.519673666615136</v>
+        <v>-6.697681700261747</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.24859810747227</v>
       </c>
       <c r="E25">
-        <v>-25.88346436098517</v>
+        <v>-27.3056633224121</v>
       </c>
       <c r="F25">
-        <v>4.648976780125704</v>
+        <v>4.359535519608159</v>
       </c>
       <c r="G25">
-        <v>-5.574671821339097</v>
+        <v>-5.519925329756169</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.918325027961738</v>
       </c>
       <c r="E26">
-        <v>-27.02472132345024</v>
+        <v>-28.29467298873929</v>
       </c>
       <c r="F26">
-        <v>4.690206979928254</v>
+        <v>4.10948577632534</v>
       </c>
       <c r="G26">
-        <v>-6.146426209790005</v>
+        <v>-6.080473521556645</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.666294425132572</v>
       </c>
       <c r="E27">
-        <v>-26.12038053564446</v>
+        <v>-26.21921900933587</v>
       </c>
       <c r="F27">
-        <v>4.574089662208234</v>
+        <v>4.216596558504256</v>
       </c>
       <c r="G27">
-        <v>-5.343373936146836</v>
+        <v>-5.001192638662227</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.495282221887005</v>
       </c>
       <c r="E28">
-        <v>-26.69902894434458</v>
+        <v>-26.60178902197788</v>
       </c>
       <c r="F28">
-        <v>4.476115279455488</v>
+        <v>4.420650730884968</v>
       </c>
       <c r="G28">
-        <v>-5.99273413312934</v>
+        <v>-5.634427168322941</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.406258281455039</v>
       </c>
       <c r="E29">
-        <v>-26.21385276763678</v>
+        <v>-27.10369791014401</v>
       </c>
       <c r="F29">
-        <v>4.373461045722618</v>
+        <v>3.702387835937968</v>
       </c>
       <c r="G29">
-        <v>-6.061126693425144</v>
+        <v>-5.060550720181359</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.384635931220745</v>
       </c>
       <c r="E30">
-        <v>-26.13907407634812</v>
+        <v>-27.14359829462559</v>
       </c>
       <c r="F30">
-        <v>4.378552660240756</v>
+        <v>3.662179126450877</v>
       </c>
       <c r="G30">
-        <v>-5.712413689591552</v>
+        <v>-5.066311069419691</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.422634105219212</v>
       </c>
       <c r="E31">
-        <v>-26.69445971407084</v>
+        <v>-26.3179487996511</v>
       </c>
       <c r="F31">
-        <v>4.169283344280503</v>
+        <v>3.794605447688092</v>
       </c>
       <c r="G31">
-        <v>-5.373539627100675</v>
+        <v>-5.585576758345455</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.511655387343055</v>
       </c>
       <c r="E32">
-        <v>-26.67443480200892</v>
+        <v>-26.78934030147955</v>
       </c>
       <c r="F32">
-        <v>4.048425994755572</v>
+        <v>3.653592272977364</v>
       </c>
       <c r="G32">
-        <v>-5.855588163073953</v>
+        <v>-5.184130074616814</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.633157339394173</v>
       </c>
       <c r="E33">
-        <v>-25.05102668347318</v>
+        <v>-26.0434779900462</v>
       </c>
       <c r="F33">
-        <v>4.006224983226858</v>
+        <v>3.491924405717474</v>
       </c>
       <c r="G33">
-        <v>-5.776095343584974</v>
+        <v>-5.081211834891951</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.778996295902799</v>
       </c>
       <c r="E34">
-        <v>-26.03130998038759</v>
+        <v>-26.95285444094851</v>
       </c>
       <c r="F34">
-        <v>4.273057258095588</v>
+        <v>3.597557590277285</v>
       </c>
       <c r="G34">
-        <v>-4.907345293714967</v>
+        <v>-5.291408302816897</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.941017843685702</v>
       </c>
       <c r="E35">
-        <v>-25.84905701547489</v>
+        <v>-25.91443912319763</v>
       </c>
       <c r="F35">
-        <v>3.959288691010979</v>
+        <v>3.509159877195202</v>
       </c>
       <c r="G35">
-        <v>-5.332733842783619</v>
+        <v>-4.767401912678896</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.103582828779808</v>
       </c>
       <c r="E36">
-        <v>-25.33563674638126</v>
+        <v>-27.36550257794946</v>
       </c>
       <c r="F36">
-        <v>3.816843846152693</v>
+        <v>3.612678814357901</v>
       </c>
       <c r="G36">
-        <v>-6.137315588465931</v>
+        <v>-5.079076533019121</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.264997145498562</v>
       </c>
       <c r="E37">
-        <v>-25.10444003439365</v>
+        <v>-24.7155211011929</v>
       </c>
       <c r="F37">
-        <v>4.135761041168396</v>
+        <v>3.372847141641497</v>
       </c>
       <c r="G37">
-        <v>-5.442038124853736</v>
+        <v>-5.633056602469683</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.423833352446631</v>
       </c>
       <c r="E38">
-        <v>-24.05239400987969</v>
+        <v>-25.60557908197849</v>
       </c>
       <c r="F38">
-        <v>3.80099253364506</v>
+        <v>3.915586326274427</v>
       </c>
       <c r="G38">
-        <v>-5.80963448044333</v>
+        <v>-5.127384013528166</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.57231199873688</v>
       </c>
       <c r="E39">
-        <v>-23.32041599975386</v>
+        <v>-24.7365966192246</v>
       </c>
       <c r="F39">
-        <v>3.992508506293236</v>
+        <v>3.6786449168537</v>
       </c>
       <c r="G39">
-        <v>-5.855568299800717</v>
+        <v>-5.122699591590098</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.718888181608349</v>
       </c>
       <c r="E40">
-        <v>-23.40349991237259</v>
+        <v>-24.57761095376331</v>
       </c>
       <c r="F40">
-        <v>3.526377927907859</v>
+        <v>3.657245882524283</v>
       </c>
       <c r="G40">
-        <v>-5.267850460759442</v>
+        <v>-6.466354020159634</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.869169598615428</v>
       </c>
       <c r="E41">
-        <v>-23.16273000633278</v>
+        <v>-24.39100159685523</v>
       </c>
       <c r="F41">
-        <v>4.197064713449142</v>
+        <v>4.131717839966279</v>
       </c>
       <c r="G41">
-        <v>-6.239800146725149</v>
+        <v>-5.519336052650178</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.020649343781091</v>
       </c>
       <c r="E42">
-        <v>-23.44773857495352</v>
+        <v>-23.35365499897016</v>
       </c>
       <c r="F42">
-        <v>3.647073739429415</v>
+        <v>3.887893644637053</v>
       </c>
       <c r="G42">
-        <v>-6.04579224648724</v>
+        <v>-6.778452390328885</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.187169590876728</v>
       </c>
       <c r="E43">
-        <v>-22.15415280381844</v>
+        <v>-21.54831090870226</v>
       </c>
       <c r="F43">
-        <v>3.689718188614453</v>
+        <v>3.681337216909947</v>
       </c>
       <c r="G43">
-        <v>-5.641961969970322</v>
+        <v>-5.886922476603154</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.375627438831357</v>
       </c>
       <c r="E44">
-        <v>-21.4508581480572</v>
+        <v>-21.08008028173117</v>
       </c>
       <c r="F44">
-        <v>3.863457062361822</v>
+        <v>3.721387555805495</v>
       </c>
       <c r="G44">
-        <v>-6.470495512629261</v>
+        <v>-6.89985009525396</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.583261568781483</v>
       </c>
       <c r="E45">
-        <v>-20.89219389515292</v>
+        <v>-21.46558021705613</v>
       </c>
       <c r="F45">
-        <v>4.070111679855684</v>
+        <v>3.43952749550516</v>
       </c>
       <c r="G45">
-        <v>-6.403417238912549</v>
+        <v>-6.699588574492367</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.822853588244975</v>
       </c>
       <c r="E46">
-        <v>-19.94010940588428</v>
+        <v>-20.43175224347503</v>
       </c>
       <c r="F46">
-        <v>4.031892104998384</v>
+        <v>3.646152022586629</v>
       </c>
       <c r="G46">
-        <v>-6.124669304505915</v>
+        <v>-6.962680939043787</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.095637940665772</v>
       </c>
       <c r="E47">
-        <v>-19.81436273963929</v>
+        <v>-20.01682175557422</v>
       </c>
       <c r="F47">
-        <v>4.066315536776377</v>
+        <v>3.537487624904667</v>
       </c>
       <c r="G47">
-        <v>-6.892259014332411</v>
+        <v>-6.777978982316769</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.395057279447375</v>
       </c>
       <c r="E48">
-        <v>-20.0417827043045</v>
+        <v>-19.42832844438142</v>
       </c>
       <c r="F48">
-        <v>4.295420769327508</v>
+        <v>3.975854254886475</v>
       </c>
       <c r="G48">
-        <v>-6.256895803889946</v>
+        <v>-6.578889394676079</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.728093110039743</v>
       </c>
       <c r="E49">
-        <v>-18.56912295701009</v>
+        <v>-20.203254501996</v>
       </c>
       <c r="F49">
-        <v>3.977167147090374</v>
+        <v>3.96143777993823</v>
       </c>
       <c r="G49">
-        <v>-7.146164615012354</v>
+        <v>-7.495192120672176</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.087261248856894</v>
       </c>
       <c r="E50">
-        <v>-17.66639883442506</v>
+        <v>-18.86720523009099</v>
       </c>
       <c r="F50">
-        <v>4.242092640036916</v>
+        <v>3.967180297587613</v>
       </c>
       <c r="G50">
-        <v>-6.135805979700023</v>
+        <v>-7.432940622351721</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.461150436472959</v>
       </c>
       <c r="E51">
-        <v>-17.966872141782</v>
+        <v>-18.32517406221689</v>
       </c>
       <c r="F51">
-        <v>4.26637877025018</v>
+        <v>3.79856154506486</v>
       </c>
       <c r="G51">
-        <v>-7.205976241270366</v>
+        <v>-7.727579175346857</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.85056841412583</v>
       </c>
       <c r="E52">
-        <v>-17.4868267261249</v>
+        <v>-17.71139375216527</v>
       </c>
       <c r="F52">
-        <v>4.150456248357759</v>
+        <v>4.275212681846501</v>
       </c>
       <c r="G52">
-        <v>-7.178627824570447</v>
+        <v>-7.610054808702729</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.242001464897324</v>
       </c>
       <c r="E53">
-        <v>-17.97845597829362</v>
+        <v>-17.60512858110128</v>
       </c>
       <c r="F53">
-        <v>3.866945966493535</v>
+        <v>4.506408406206013</v>
       </c>
       <c r="G53">
-        <v>-7.106815470732577</v>
+        <v>-7.645282323786113</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.624698820275587</v>
       </c>
       <c r="E54">
-        <v>-16.7561665019353</v>
+        <v>-17.87535168208698</v>
       </c>
       <c r="F54">
-        <v>4.100583765374656</v>
+        <v>4.25785368130737</v>
       </c>
       <c r="G54">
-        <v>-7.449562871504401</v>
+        <v>-7.779359418126597</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.998331186611145</v>
       </c>
       <c r="E55">
-        <v>-16.09204767481441</v>
+        <v>-16.23218583145578</v>
       </c>
       <c r="F55">
-        <v>3.904354683922131</v>
+        <v>4.202143658319956</v>
       </c>
       <c r="G55">
-        <v>-8.010316317128312</v>
+        <v>-8.626710101630753</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.34857961837932</v>
       </c>
       <c r="E56">
-        <v>-15.3929056297182</v>
+        <v>-15.3208802506262</v>
       </c>
       <c r="F56">
-        <v>4.228692904286383</v>
+        <v>3.91193905155117</v>
       </c>
       <c r="G56">
-        <v>-7.974698157671293</v>
+        <v>-9.077308454980955</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.67045274324224</v>
       </c>
       <c r="E57">
-        <v>-15.26276181521176</v>
+        <v>-16.24498329900145</v>
       </c>
       <c r="F57">
-        <v>4.397148535099846</v>
+        <v>4.154852615979019</v>
       </c>
       <c r="G57">
-        <v>-7.999282268845921</v>
+        <v>-7.988470027114661</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.96689131946439</v>
       </c>
       <c r="E58">
-        <v>-14.6323710625</v>
+        <v>-16.28474782926281</v>
       </c>
       <c r="F58">
-        <v>3.913004885632261</v>
+        <v>3.685206210461366</v>
       </c>
       <c r="G58">
-        <v>-7.621661581363414</v>
+        <v>-9.567845229716923</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.22639456191246</v>
       </c>
       <c r="E59">
-        <v>-14.70352697458252</v>
+        <v>-14.25976822114888</v>
       </c>
       <c r="F59">
-        <v>4.142352425188455</v>
+        <v>4.057402439884283</v>
       </c>
       <c r="G59">
-        <v>-7.461709263087987</v>
+        <v>-9.908367943886358</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.45307185553934</v>
       </c>
       <c r="E60">
-        <v>-14.74546970084157</v>
+        <v>-15.8651575416081</v>
       </c>
       <c r="F60">
-        <v>4.111185092772606</v>
+        <v>3.941481501697778</v>
       </c>
       <c r="G60">
-        <v>-8.091308813746581</v>
+        <v>-9.093768487402212</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.65308338425893</v>
       </c>
       <c r="E61">
-        <v>-14.56024605697983</v>
+        <v>-14.49753122044761</v>
       </c>
       <c r="F61">
-        <v>4.078028625726967</v>
+        <v>4.068125712637723</v>
       </c>
       <c r="G61">
-        <v>-8.314055559810903</v>
+        <v>-9.570261927960592</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.81640226741943</v>
       </c>
       <c r="E62">
-        <v>-15.30439207676427</v>
+        <v>-14.80017819532823</v>
       </c>
       <c r="F62">
-        <v>4.097136037596743</v>
+        <v>3.643396374293765</v>
       </c>
       <c r="G62">
-        <v>-8.455624418706758</v>
+        <v>-9.827567458909366</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.95420753393748</v>
       </c>
       <c r="E63">
-        <v>-14.16521368386872</v>
+        <v>-14.08550801285972</v>
       </c>
       <c r="F63">
-        <v>4.083967522909864</v>
+        <v>4.175078124225096</v>
       </c>
       <c r="G63">
-        <v>-7.980031446535059</v>
+        <v>-10.65640226121238</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.07257974164069</v>
       </c>
       <c r="E64">
-        <v>-13.92918961858895</v>
+        <v>-13.94072364188648</v>
       </c>
       <c r="F64">
-        <v>4.316013697345968</v>
+        <v>4.356070371065178</v>
       </c>
       <c r="G64">
-        <v>-9.263006885915294</v>
+        <v>-10.16839474326841</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.16075902839405</v>
       </c>
       <c r="E65">
-        <v>-13.52932989218566</v>
+        <v>-14.28138262758749</v>
       </c>
       <c r="F65">
-        <v>4.239508031982919</v>
+        <v>3.776581290664476</v>
       </c>
       <c r="G65">
-        <v>-8.577753754196012</v>
+        <v>-9.502663898594212</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.23347249424731</v>
       </c>
       <c r="E66">
-        <v>-13.64410859438407</v>
+        <v>-14.22493972755589</v>
       </c>
       <c r="F66">
-        <v>4.400422055227059</v>
+        <v>3.570575992595943</v>
       </c>
       <c r="G66">
-        <v>-8.742837418057308</v>
+        <v>-9.375366801518158</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.29367654767775</v>
       </c>
       <c r="E67">
-        <v>-13.62386178709578</v>
+        <v>-13.76927108748207</v>
       </c>
       <c r="F67">
-        <v>4.276338696752378</v>
+        <v>4.301963058464189</v>
       </c>
       <c r="G67">
-        <v>-9.277381274646809</v>
+        <v>-9.940824532353373</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.33004925693128</v>
       </c>
       <c r="E68">
-        <v>-11.92117367410776</v>
+        <v>-15.3649830589869</v>
       </c>
       <c r="F68">
-        <v>3.71933032182134</v>
+        <v>4.130035944284082</v>
       </c>
       <c r="G68">
-        <v>-8.842690092612806</v>
+        <v>-10.08958389616052</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.35814163931119</v>
       </c>
       <c r="E69">
-        <v>-13.43286433887427</v>
+        <v>-13.68295837289588</v>
       </c>
       <c r="F69">
-        <v>3.963457004980415</v>
+        <v>3.645008586915682</v>
       </c>
       <c r="G69">
-        <v>-9.391628201207057</v>
+        <v>-10.06238776455541</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.37643857450566</v>
       </c>
       <c r="E70">
-        <v>-13.67044167073868</v>
+        <v>-14.34678737768028</v>
       </c>
       <c r="F70">
-        <v>3.786259317513726</v>
+        <v>4.247125657436182</v>
       </c>
       <c r="G70">
-        <v>-9.67033640906722</v>
+        <v>-9.263314766650446</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.37489020868348</v>
       </c>
       <c r="E71">
-        <v>-13.02111283972684</v>
+        <v>-13.96626423528974</v>
       </c>
       <c r="F71">
-        <v>3.755967774469116</v>
+        <v>3.289799187141768</v>
       </c>
       <c r="G71">
-        <v>-8.97276804794185</v>
+        <v>-9.82078084055386</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.36674414199355</v>
       </c>
       <c r="E72">
-        <v>-13.82683252059357</v>
+        <v>-13.94085949610671</v>
       </c>
       <c r="F72">
-        <v>3.917681569200553</v>
+        <v>3.655565570548001</v>
       </c>
       <c r="G72">
-        <v>-9.078841237565637</v>
+        <v>-9.393031872515708</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.34646741450366</v>
       </c>
       <c r="E73">
-        <v>-13.37501761190029</v>
+        <v>-13.40015969959087</v>
       </c>
       <c r="F73">
-        <v>3.674742665478058</v>
+        <v>3.353055568816251</v>
       </c>
       <c r="G73">
-        <v>-8.901564834483205</v>
+        <v>-8.12488767715141</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.30730153183381</v>
       </c>
       <c r="E74">
-        <v>-13.30436436043261</v>
+        <v>-12.86158828585864</v>
       </c>
       <c r="F74">
-        <v>3.417746788050121</v>
+        <v>3.282940156822</v>
       </c>
       <c r="G74">
-        <v>-9.207568490314658</v>
+        <v>-8.601096410793412</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.26117213636162</v>
       </c>
       <c r="E75">
-        <v>-14.088034901356</v>
+        <v>-13.27618819515689</v>
       </c>
       <c r="F75">
-        <v>3.772387637400392</v>
+        <v>3.56566333684625</v>
       </c>
       <c r="G75">
-        <v>-8.270521885969488</v>
+        <v>-9.78399074797594</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.20197397990466</v>
       </c>
       <c r="E76">
-        <v>-13.93419811084143</v>
+        <v>-12.74411061315165</v>
       </c>
       <c r="F76">
-        <v>3.48499094121968</v>
+        <v>2.994355681204708</v>
       </c>
       <c r="G76">
-        <v>-8.081579120406664</v>
+        <v>-9.226203551155216</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.12893584408492</v>
       </c>
       <c r="E77">
-        <v>-14.92336627375889</v>
+        <v>-15.45510422021355</v>
       </c>
       <c r="F77">
-        <v>2.96621322708735</v>
+        <v>3.090432784270758</v>
       </c>
       <c r="G77">
-        <v>-8.490014365768706</v>
+        <v>-8.983328688212124</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.0544889527569</v>
       </c>
       <c r="E78">
-        <v>-14.20544011847886</v>
+        <v>-15.60741491498753</v>
       </c>
       <c r="F78">
-        <v>3.466342804065381</v>
+        <v>3.273439505035279</v>
       </c>
       <c r="G78">
-        <v>-7.515724124106736</v>
+        <v>-9.549902072894074</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.97232117705372</v>
       </c>
       <c r="E79">
-        <v>-15.04409539080338</v>
+        <v>-16.34038918939505</v>
       </c>
       <c r="F79">
-        <v>3.269863497078216</v>
+        <v>3.400284846626486</v>
       </c>
       <c r="G79">
-        <v>-8.165180326909878</v>
+        <v>-8.27641465702939</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.8867420631884</v>
       </c>
       <c r="E80">
-        <v>-14.63146083922446</v>
+        <v>-15.74604508978435</v>
       </c>
       <c r="F80">
-        <v>3.666094047473843</v>
+        <v>3.37218990368659</v>
       </c>
       <c r="G80">
-        <v>-8.080268144373113</v>
+        <v>-7.346015628127077</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.80817390120459</v>
       </c>
       <c r="E81">
-        <v>-15.58131731928133</v>
+        <v>-17.91213194797728</v>
       </c>
       <c r="F81">
-        <v>3.573458337362043</v>
+        <v>2.816868175555494</v>
       </c>
       <c r="G81">
-        <v>-7.924298412381429</v>
+        <v>-7.559486225590361</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.72779338484338</v>
       </c>
       <c r="E82">
-        <v>-18.44930859171515</v>
+        <v>-17.46378132189986</v>
       </c>
       <c r="F82">
-        <v>3.490435722156961</v>
+        <v>3.168283015956015</v>
       </c>
       <c r="G82">
-        <v>-6.876732555753229</v>
+        <v>-7.60096405065189</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.6522543199277</v>
       </c>
       <c r="E83">
-        <v>-17.89731478102418</v>
+        <v>-17.03431443243442</v>
       </c>
       <c r="F83">
-        <v>3.397730328984882</v>
+        <v>3.135587407331768</v>
       </c>
       <c r="G83">
-        <v>-7.201861233165053</v>
+        <v>-7.748468717699657</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.58746116594045</v>
       </c>
       <c r="E84">
-        <v>-18.96857059227868</v>
+        <v>-18.61610587483968</v>
       </c>
       <c r="F84">
-        <v>2.955048100383501</v>
+        <v>2.617786839749263</v>
       </c>
       <c r="G84">
-        <v>-6.396835874380478</v>
+        <v>-6.606065663007956</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.52031237477427</v>
       </c>
       <c r="E85">
-        <v>-20.41794945469965</v>
+        <v>-20.22918907263793</v>
       </c>
       <c r="F85">
-        <v>3.102706505115414</v>
+        <v>3.223581275405414</v>
       </c>
       <c r="G85">
-        <v>-7.07931476893785</v>
+        <v>-6.943145409816548</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.4580167232909</v>
       </c>
       <c r="E86">
-        <v>-21.40329558555463</v>
+        <v>-21.62644519923061</v>
       </c>
       <c r="F86">
-        <v>3.003126244564412</v>
+        <v>2.954275251896767</v>
       </c>
       <c r="G86">
-        <v>-6.928516109078509</v>
+        <v>-5.723931077522677</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.40073271800028</v>
       </c>
       <c r="E87">
-        <v>-21.46625948815728</v>
+        <v>-22.37057310511901</v>
       </c>
       <c r="F87">
-        <v>2.962310975711707</v>
+        <v>3.196243343893098</v>
       </c>
       <c r="G87">
-        <v>-6.112714924563607</v>
+        <v>-6.191793925860178</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.33089199623327</v>
       </c>
       <c r="E88">
-        <v>-22.71872671530272</v>
+        <v>-23.14744640655689</v>
       </c>
       <c r="F88">
-        <v>2.855380736007151</v>
+        <v>3.060660696766412</v>
       </c>
       <c r="G88">
-        <v>-5.957589381684437</v>
+        <v>-5.905107303250372</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.25446420039867</v>
       </c>
       <c r="E89">
-        <v>-25.76736787285053</v>
+        <v>-25.15009158086498</v>
       </c>
       <c r="F89">
-        <v>2.883133598469311</v>
+        <v>2.873012133963738</v>
       </c>
       <c r="G89">
-        <v>-6.045577061027187</v>
+        <v>-6.214623447898991</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.16315234968734</v>
       </c>
       <c r="E90">
-        <v>-26.95092983949525</v>
+        <v>-25.62420922404604</v>
       </c>
       <c r="F90">
-        <v>2.376832319538813</v>
+        <v>3.193647649897693</v>
       </c>
       <c r="G90">
-        <v>-6.273643853773119</v>
+        <v>-6.498909924992827</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.03594258506951</v>
       </c>
       <c r="E91">
-        <v>-27.44025862686808</v>
+        <v>-28.55209409370531</v>
       </c>
       <c r="F91">
-        <v>2.820393504923262</v>
+        <v>3.17219160215532</v>
       </c>
       <c r="G91">
-        <v>-5.935872202946818</v>
+        <v>-5.930250896621136</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.87362145482518</v>
       </c>
       <c r="E92">
-        <v>-29.48798702415953</v>
+        <v>-30.26997750122607</v>
       </c>
       <c r="F92">
-        <v>2.688695688407149</v>
+        <v>3.07752082994218</v>
       </c>
       <c r="G92">
-        <v>-5.908851530255287</v>
+        <v>-6.418341178203583</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.66184009244188</v>
       </c>
       <c r="E93">
-        <v>-31.98109084010537</v>
+        <v>-31.55517653849895</v>
       </c>
       <c r="F93">
-        <v>2.396766425896449</v>
+        <v>2.798137685693592</v>
       </c>
       <c r="G93">
-        <v>-5.627114173226691</v>
+        <v>-4.945227866320848</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.38148716356103</v>
       </c>
       <c r="E94">
-        <v>-33.48474119927126</v>
+        <v>-33.12148512827198</v>
       </c>
       <c r="F94">
-        <v>2.406655085632453</v>
+        <v>2.404772059298995</v>
       </c>
       <c r="G94">
-        <v>-5.629815578386737</v>
+        <v>-5.625386068455192</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.03623741218529</v>
       </c>
       <c r="E95">
-        <v>-35.39742597317998</v>
+        <v>-34.99519559063368</v>
       </c>
       <c r="F95">
-        <v>2.333893301053503</v>
+        <v>2.523557921486531</v>
       </c>
       <c r="G95">
-        <v>-5.271756904495783</v>
+        <v>-5.435274680317004</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.613440500110947</v>
       </c>
       <c r="E96">
-        <v>-37.25547923666016</v>
+        <v>-37.75629449835345</v>
       </c>
       <c r="F96">
-        <v>2.276517219443047</v>
+        <v>2.33462022206869</v>
       </c>
       <c r="G96">
-        <v>-5.643150455818921</v>
+        <v>-5.121352199555614</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.115196611881126</v>
       </c>
       <c r="E97">
-        <v>-39.1802776785394</v>
+        <v>-39.78701847574609</v>
       </c>
       <c r="F97">
-        <v>2.020135819910302</v>
+        <v>2.28560769139767</v>
       </c>
       <c r="G97">
-        <v>-5.570444254685447</v>
+        <v>-5.324222430202153</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.546137016971793</v>
       </c>
       <c r="E98">
-        <v>-42.07606925290631</v>
+        <v>-41.93334760184356</v>
       </c>
       <c r="F98">
-        <v>2.098271118660338</v>
+        <v>1.902857645754264</v>
       </c>
       <c r="G98">
-        <v>-5.780157382961659</v>
+        <v>-5.232364723123995</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.930108709777694</v>
       </c>
       <c r="E99">
-        <v>-45.29013103748031</v>
+        <v>-42.90767369120088</v>
       </c>
       <c r="F99">
-        <v>1.836470277484958</v>
+        <v>1.793936687714001</v>
       </c>
       <c r="G99">
-        <v>-5.584126739399255</v>
+        <v>-5.2328877893192</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.257056748842367</v>
       </c>
       <c r="E100">
-        <v>-46.83569695206119</v>
+        <v>-46.42313259182939</v>
       </c>
       <c r="F100">
-        <v>1.947576749688528</v>
+        <v>1.847286988887409</v>
       </c>
       <c r="G100">
-        <v>-6.133673988372733</v>
+        <v>-6.454349982034236</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.59697877104739</v>
       </c>
       <c r="E101">
-        <v>-48.11384289106712</v>
+        <v>-48.04378739816846</v>
       </c>
       <c r="F101">
-        <v>1.414678713614139</v>
+        <v>2.019534011662434</v>
       </c>
       <c r="G101">
-        <v>-5.841558071078522</v>
+        <v>-5.18709632342</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.894118119682939</v>
       </c>
       <c r="E102">
-        <v>-50.69963211664645</v>
+        <v>-50.82509462114746</v>
       </c>
       <c r="F102">
-        <v>1.462775862266035</v>
+        <v>1.432669612813531</v>
       </c>
       <c r="G102">
-        <v>-5.941645794367307</v>
+        <v>-6.077328503294337</v>
       </c>
     </row>
   </sheetData>
